--- a/data/trans_dic/IP18_E_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18_E_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,93; 95,38</t>
+          <t>82,34; 95,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,67; 98,23</t>
+          <t>85,73; 98,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,4; 91,12</t>
+          <t>75,02; 90,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,18; 95,25</t>
+          <t>60,44; 95,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,03; 92,03</t>
+          <t>74,99; 92,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,8; 98,99</t>
+          <t>91,47; 98,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,26; 95,73</t>
+          <t>83,5; 95,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,4; 100,0</t>
+          <t>75,58; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,26; 92,41</t>
+          <t>81,56; 92,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91,51; 98,27</t>
+          <t>91,14; 98,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82,61; 91,97</t>
+          <t>82,24; 91,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,1; 95,9</t>
+          <t>77,3; 96,15</t>
         </is>
       </c>
     </row>
@@ -857,37 +857,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,05; 99,31</t>
+          <t>93,58; 99,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,66; 96,52</t>
+          <t>87,73; 96,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,22; 98,73</t>
+          <t>93,08; 98,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71,15; 100,0</t>
+          <t>71,96; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,59; 94,55</t>
+          <t>84,29; 94,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,09; 95,78</t>
+          <t>85,88; 95,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,18; 100,0</t>
+          <t>94,9; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90,26; 96,02</t>
+          <t>90,07; 96,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89,04; 95,54</t>
+          <t>88,52; 95,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95,35; 99,02</t>
+          <t>95,22; 98,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,53; 100,0</t>
+          <t>86,54; 100,0</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,71; 98,73</t>
+          <t>87,86; 98,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,93; 97,81</t>
+          <t>87,02; 97,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,01; 98,71</t>
+          <t>87,1; 98,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,74; 90,79</t>
+          <t>57,14; 91,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90,67; 99,08</t>
+          <t>91,55; 99,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,81; 98,03</t>
+          <t>89,75; 98,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,28; 95,85</t>
+          <t>84,18; 95,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,8; 98,21</t>
+          <t>91,66; 97,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90,57; 97,34</t>
+          <t>90,16; 97,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88,25; 96,37</t>
+          <t>88,12; 96,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76,95; 95,91</t>
+          <t>76,83; 95,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,54; 96,34</t>
+          <t>84,91; 96,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,63; 99,4</t>
+          <t>93,73; 99,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,48; 99,09</t>
+          <t>90,79; 99,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76,07; 100,0</t>
+          <t>72,98; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,84; 96,32</t>
+          <t>84,98; 96,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,18; 100,0</t>
+          <t>93,59; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,04; 95,67</t>
+          <t>85,78; 95,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,31; 100,0</t>
+          <t>82,31; 100,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,84; 95,48</t>
+          <t>87,94; 95,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95,22; 99,27</t>
+          <t>95,35; 99,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90,26; 96,65</t>
+          <t>90,07; 96,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,5; 98,5</t>
+          <t>85,03; 98,59</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>85,16; 100,0</t>
+          <t>85,55; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,79; 100,0</t>
+          <t>88,64; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,7; 98,4</t>
+          <t>86,97; 98,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,52; 100,0</t>
+          <t>88,54; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,19; 98,37</t>
+          <t>86,43; 98,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,69; 100,0</t>
+          <t>92,81; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,3; 100,0</t>
+          <t>44,8; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,9; 98,85</t>
+          <t>90,67; 98,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90,36; 98,27</t>
+          <t>90,13; 98,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92,99; 99,22</t>
+          <t>92,55; 99,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,94; 94,13</t>
+          <t>57,45; 94,25</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,8; 96,16</t>
+          <t>84,76; 97,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88,07; 98,66</t>
+          <t>88,62; 98,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,23; 100,0</t>
+          <t>92,42; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,17 +1437,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,73; 97,6</t>
+          <t>86,37; 97,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,33; 98,47</t>
+          <t>87,74; 98,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,06; 98,6</t>
+          <t>87,33; 98,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,32; 96,17</t>
+          <t>87,57; 96,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90,35; 97,74</t>
+          <t>90,79; 97,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91,59; 98,57</t>
+          <t>91,06; 98,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,9; 93,79</t>
+          <t>85,15; 94,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,45; 95,28</t>
+          <t>86,6; 95,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,99; 97,47</t>
+          <t>90,29; 97,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,89; 85,25</t>
+          <t>40,2; 84,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,7; 95,61</t>
+          <t>87,13; 95,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,16; 96,78</t>
+          <t>90,64; 97,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,04; 98,83</t>
+          <t>93,23; 98,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,32; 93,7</t>
+          <t>69,21; 93,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>88,11; 93,95</t>
+          <t>88,23; 94,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90,23; 95,31</t>
+          <t>90,22; 95,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93,02; 97,48</t>
+          <t>92,83; 97,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,54; 85,92</t>
+          <t>58,4; 86,46</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,58; 97,94</t>
+          <t>91,91; 98,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>93,16; 98,55</t>
+          <t>93,31; 98,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,11; 95,58</t>
+          <t>88,9; 95,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74,42; 100,0</t>
+          <t>71,9; 100,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>93,3; 98,45</t>
+          <t>93,19; 98,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,13; 96,22</t>
+          <t>89,61; 96,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,67; 94,68</t>
+          <t>87,45; 94,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>79,63; 100,0</t>
+          <t>74,18; 100,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>93,77; 97,73</t>
+          <t>93,65; 97,56</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92,47; 96,67</t>
+          <t>92,92; 96,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89,9; 94,69</t>
+          <t>89,21; 94,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>85,09; 100,0</t>
+          <t>84,31; 100,0</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>91,89; 95,08</t>
+          <t>91,94; 94,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>93,15; 96,03</t>
+          <t>93,02; 96,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92,44; 95,38</t>
+          <t>92,38; 95,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74,35; 89,42</t>
+          <t>73,68; 89,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>91,27; 94,52</t>
+          <t>91,21; 94,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>93,05; 95,87</t>
+          <t>92,94; 95,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92,6; 95,5</t>
+          <t>92,6; 95,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>89,6; 96,71</t>
+          <t>89,59; 96,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92,03; 94,35</t>
+          <t>92,0; 94,39</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93,66; 95,71</t>
+          <t>93,75; 95,66</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92,98; 95,07</t>
+          <t>92,93; 95,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>84,51; 92,72</t>
+          <t>84,54; 92,72</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40086; 46664</t>
+          <t>40288; 46693</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46566; 53390</t>
+          <t>46595; 53411</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41591; 49606</t>
+          <t>40841; 49207</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7155; 11517</t>
+          <t>7308; 11530</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38430; 47136</t>
+          <t>38405; 47290</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56451; 61540</t>
+          <t>56870; 61544</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48211; 55432</t>
+          <t>48350; 55119</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10463; 14064</t>
+          <t>10629; 14064</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81373; 92545</t>
+          <t>81679; 92621</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>106633; 114512</t>
+          <t>106194; 114198</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92803; 103316</t>
+          <t>92388; 103180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19643; 25083</t>
+          <t>20218; 25149</t>
         </is>
       </c>
     </row>
@@ -2417,37 +2417,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83697; 89325</t>
+          <t>84177; 89329</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83529; 91970</t>
+          <t>83591; 92158</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83292; 89172</t>
+          <t>84068; 89190</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9697; 13629</t>
+          <t>9808; 13629</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80218; 89660</t>
+          <t>79930; 89406</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83916; 93362</t>
+          <t>83712; 93394</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89915; 94470</t>
+          <t>89656; 94470</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2457,22 +2457,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>166787; 177421</t>
+          <t>166433; 177558</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>171642; 184166</t>
+          <t>170639; 183680</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>176204; 182970</t>
+          <t>175953; 182915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25922; 29959</t>
+          <t>25926; 29959</t>
         </is>
       </c>
     </row>
@@ -2625,37 +2625,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54961; 61866</t>
+          <t>55055; 61868</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57320; 63761</t>
+          <t>56728; 63774</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58145; 65216</t>
+          <t>57542; 65224</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7779; 12671</t>
+          <t>7975; 12767</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>60889; 66534</t>
+          <t>61475; 66534</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62051; 68493</t>
+          <t>62705; 68502</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52925; 60190</t>
+          <t>52860; 60074</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2665,22 +2665,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119170; 127485</t>
+          <t>118984; 127114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122315; 131468</t>
+          <t>121764; 131563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113728; 124186</t>
+          <t>113551; 123903</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23378; 29136</t>
+          <t>23340; 29107</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57651; 64930</t>
+          <t>57228; 65176</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67728; 71903</t>
+          <t>67796; 71911</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65020; 71212</t>
+          <t>65246; 71176</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10093; 13268</t>
+          <t>9684; 13268</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56240; 63845</t>
+          <t>56330; 63874</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74621; 79229</t>
+          <t>74153; 79229</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67297; 75706</t>
+          <t>67882; 75791</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12242; 14695</t>
+          <t>12096; 14695</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>117424; 127641</t>
+          <t>117559; 127802</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>144323; 150456</t>
+          <t>144512; 150459</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>136291; 145945</t>
+          <t>136005; 145721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23629; 27545</t>
+          <t>23778; 27569</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25724; 30207</t>
+          <t>25842; 30207</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35706; 40214</t>
+          <t>35644; 40214</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36247; 41139</t>
+          <t>36361; 41179</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27257; 30791</t>
+          <t>27263; 30791</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36743; 41937</t>
+          <t>36848; 41938</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40647; 44330</t>
+          <t>41143; 44330</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2427; 5357</t>
+          <t>2400; 5357</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54835; 60296</t>
+          <t>55307; 60299</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74857; 81413</t>
+          <t>74668; 81397</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80102; 85470</t>
+          <t>79720; 85468</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5216; 8776</t>
+          <t>5357; 8788</t>
         </is>
       </c>
     </row>
@@ -3249,17 +3249,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41764; 47926</t>
+          <t>42242; 48414</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48669; 54519</t>
+          <t>48969; 54518</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47056; 51580</t>
+          <t>47670; 51580</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3269,17 +3269,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43531; 48988</t>
+          <t>43353; 48987</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50907; 57401</t>
+          <t>51147; 57398</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46412; 52566</t>
+          <t>46556; 52593</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3289,17 +3289,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87343; 96197</t>
+          <t>87599; 96396</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102600; 110990</t>
+          <t>103094; 111171</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96073; 103393</t>
+          <t>95515; 103368</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>102106; 112787</t>
+          <t>102408; 113420</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>115985; 126383</t>
+          <t>114863; 126257</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100375; 108729</t>
+          <t>100716; 108483</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8224; 19003</t>
+          <t>8962; 18796</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106850; 116480</t>
+          <t>106147; 116475</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>129004; 138471</t>
+          <t>129687; 139145</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>105614; 112187</t>
+          <t>105831; 112202</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18666; 25979</t>
+          <t>19189; 25967</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>213309; 227448</t>
+          <t>213604; 227825</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>248781; 262778</t>
+          <t>248746; 263185</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>209343; 219390</t>
+          <t>208926; 219064</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28779; 42976</t>
+          <t>29210; 43243</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>109657; 117268</t>
+          <t>110057; 117383</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>140435; 148560</t>
+          <t>140656; 148441</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>141860; 152155</t>
+          <t>141521; 151923</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8914; 11978</t>
+          <t>8612; 11978</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>122245; 128995</t>
+          <t>122106; 128993</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>143346; 153038</t>
+          <t>142518; 153375</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>143418; 154902</t>
+          <t>143071; 154813</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15880; 19942</t>
+          <t>14793; 19942</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>235150; 245082</t>
+          <t>234841; 244649</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>286476; 299460</t>
+          <t>287856; 299732</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>290174; 305638</t>
+          <t>287970; 304309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>27162; 31920</t>
+          <t>26911; 31920</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>541227; 559988</t>
+          <t>541509; 559492</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>620381; 639591</t>
+          <t>619523; 640023</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>597946; 616934</t>
+          <t>597539; 616918</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74582; 89702</t>
+          <t>73912; 89845</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>559770; 579694</t>
+          <t>559408; 579792</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>662339; 682374</t>
+          <t>661538; 682051</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>619551; 638985</t>
+          <t>619529; 638715</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>117908; 127257</t>
+          <t>117893; 127020</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1106523; 1134395</t>
+          <t>1106063; 1134911</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1290435; 1318748</t>
+          <t>1291657; 1317988</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1223471; 1251004</t>
+          <t>1222887; 1251511</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>195974; 215015</t>
+          <t>196061; 215028</t>
         </is>
       </c>
     </row>
